--- a/branches/dev/CodeSystem-selftest-palette.xlsx
+++ b/branches/dev/CodeSystem-selftest-palette.xlsx
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Self-Test Palette</t>
+    <t>Selbsttest-Palette</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T18:16:44+00:00</t>
+    <t>2026-07-22T18:56:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Two arbitrary codes so the self-test IG renders a CodeSystem page; not an MII artifact.</t>
+    <t>Zwei beliebige Codes, damit die Selbsttest-IG eine CodeSystem-Seite rendert; kein MII-Artefakt.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -141,19 +141,19 @@
     <t>primary</t>
   </si>
   <si>
-    <t>Primary</t>
-  </si>
-  <si>
-    <t>Stands in for the template's primary brand colour slot.</t>
+    <t>Primärfarbe</t>
+  </si>
+  <si>
+    <t>Platzhalter für den Steckplatz der primären Markenfarbe der Vorlage.</t>
   </si>
   <si>
     <t>accent</t>
   </si>
   <si>
-    <t>Accent</t>
-  </si>
-  <si>
-    <t>Stands in for the template's accent colour slot.</t>
+    <t>Akzentfarbe</t>
+  </si>
+  <si>
+    <t>Platzhalter für den Steckplatz der Akzentfarbe der Vorlage.</t>
   </si>
 </sst>
 </file>

--- a/branches/dev/CodeSystem-selftest-palette.xlsx
+++ b/branches/dev/CodeSystem-selftest-palette.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T18:56:05+00:00</t>
+    <t>2026-07-23T04:43:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/CodeSystem-selftest-palette.xlsx
+++ b/branches/dev/CodeSystem-selftest-palette.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T04:43:54+00:00</t>
+    <t>2026-07-23T04:54:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/CodeSystem-selftest-palette.xlsx
+++ b/branches/dev/CodeSystem-selftest-palette.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T04:54:47+00:00</t>
+    <t>2026-07-23T09:06:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/CodeSystem-selftest-palette.xlsx
+++ b/branches/dev/CodeSystem-selftest-palette.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T09:06:16+00:00</t>
+    <t>2026-07-23T11:07:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/CodeSystem-selftest-palette.xlsx
+++ b/branches/dev/CodeSystem-selftest-palette.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T11:07:49+00:00</t>
+    <t>2026-07-23T22:28:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
